--- a/plot/storage/output/ongoing/ongoing_tech_filter_q.xlsx
+++ b/plot/storage/output/ongoing/ongoing_tech_filter_q.xlsx
@@ -459,7 +459,7 @@
         <v>162462626.5714286</v>
       </c>
       <c r="C2" t="n">
-        <v>226574838.6388889</v>
+        <v>191574838.6388889</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +470,7 @@
         <v>91335161.23809524</v>
       </c>
       <c r="C3" t="n">
-        <v>191829941.75</v>
+        <v>152941052.8611111</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>55771428.57142857</v>
       </c>
       <c r="C4" t="n">
-        <v>202253333.3333333</v>
+        <v>155586666.6666667</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +492,7 @@
         <v>163026511.3214286</v>
       </c>
       <c r="C5" t="n">
-        <v>278642222.2222222</v>
+        <v>225308888.8888889</v>
       </c>
     </row>
     <row r="6">
@@ -503,7 +503,7 @@
         <v>206573530.9929972</v>
       </c>
       <c r="C6" t="n">
-        <v>330586666.6666666</v>
+        <v>305586666.6666667</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +514,7 @@
         <v>241273651.6694678</v>
       </c>
       <c r="C7" t="n">
-        <v>330586666.6666666</v>
+        <v>305586666.6666667</v>
       </c>
     </row>
     <row r="8">
@@ -525,7 +525,7 @@
         <v>252386796.39169</v>
       </c>
       <c r="C8" t="n">
-        <v>345387500</v>
+        <v>320387500</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         <v>569686229.3617754</v>
       </c>
       <c r="C9" t="n">
-        <v>471211622.8070176</v>
+        <v>427461622.8070176</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>510329028.230823</v>
       </c>
       <c r="C10" t="n">
-        <v>616869517.5438597</v>
+        <v>535619517.5438596</v>
       </c>
     </row>
     <row r="11">
@@ -558,7 +558,7 @@
         <v>502819107.5959024</v>
       </c>
       <c r="C11" t="n">
-        <v>588279239.7660818</v>
+        <v>507029239.7660819</v>
       </c>
     </row>
     <row r="12">
@@ -569,7 +569,7 @@
         <v>507888552.0403469</v>
       </c>
       <c r="C12" t="n">
-        <v>934499833.6688597</v>
+        <v>853249833.6688596</v>
       </c>
     </row>
     <row r="13">
@@ -580,7 +580,7 @@
         <v>931556370.8124057</v>
       </c>
       <c r="C13" t="n">
-        <v>978349093.4902883</v>
+        <v>900432426.8236215</v>
       </c>
     </row>
     <row r="14">
@@ -591,7 +591,7 @@
         <v>969758985.1914907</v>
       </c>
       <c r="C14" t="n">
-        <v>1584839110.322248</v>
+        <v>1513589110.322248</v>
       </c>
     </row>
     <row r="15">
@@ -602,7 +602,7 @@
         <v>1009318335.691491</v>
       </c>
       <c r="C15" t="n">
-        <v>1609720574.890961</v>
+        <v>1542359463.77985</v>
       </c>
     </row>
     <row r="16">
@@ -613,7 +613,7 @@
         <v>1058952463.39784</v>
       </c>
       <c r="C16" t="n">
-        <v>1612673415.324306</v>
+        <v>1553090081.990973</v>
       </c>
     </row>
     <row r="17">
@@ -624,7 +624,7 @@
         <v>1002868033.14784</v>
       </c>
       <c r="C17" t="n">
-        <v>1504832959.550973</v>
+        <v>1442749626.21764</v>
       </c>
     </row>
     <row r="18">
@@ -635,7 +635,7 @@
         <v>1018639099.912637</v>
       </c>
       <c r="C18" t="n">
-        <v>1271731413.083672</v>
+        <v>1204648079.750338</v>
       </c>
     </row>
     <row r="19">
@@ -646,7 +646,7 @@
         <v>1236569142.875172</v>
       </c>
       <c r="C19" t="n">
-        <v>1287604428.956688</v>
+        <v>1220521095.623354</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>1229618031.764061</v>
       </c>
       <c r="C20" t="n">
-        <v>1367815790.148607</v>
+        <v>1288510234.593051</v>
       </c>
     </row>
     <row r="21">
@@ -668,7 +668,7 @@
         <v>1140514575.625172</v>
       </c>
       <c r="C21" t="n">
-        <v>1543885234.593051</v>
+        <v>1477218567.926384</v>
       </c>
     </row>
     <row r="22">
@@ -679,7 +679,7 @@
         <v>808374351.2661978</v>
       </c>
       <c r="C22" t="n">
-        <v>1181974978.182795</v>
+        <v>1152808311.516128</v>
       </c>
     </row>
     <row r="23">
@@ -690,7 +690,7 @@
         <v>1160876898.13689</v>
       </c>
       <c r="C23" t="n">
-        <v>799565671.1758018</v>
+        <v>770399004.5091351</v>
       </c>
     </row>
     <row r="24">
@@ -701,7 +701,7 @@
         <v>1240206827.678319</v>
       </c>
       <c r="C24" t="n">
-        <v>903890086.4695081</v>
+        <v>874723419.8028414</v>
       </c>
     </row>
     <row r="25">
@@ -712,7 +712,7 @@
         <v>1167219759.168345</v>
       </c>
       <c r="C25" t="n">
-        <v>873060706.9972858</v>
+        <v>840560706.9972858</v>
       </c>
     </row>
     <row r="26">
@@ -723,7 +723,7 @@
         <v>1360206062.397019</v>
       </c>
       <c r="C26" t="n">
-        <v>872745888.2263768</v>
+        <v>833579221.5597101</v>
       </c>
     </row>
     <row r="27">
@@ -734,7 +734,7 @@
         <v>1494771925.572232</v>
       </c>
       <c r="C27" t="n">
-        <v>1064973978.453289</v>
+        <v>1025807311.786622</v>
       </c>
     </row>
     <row r="28">
@@ -742,10 +742,10 @@
         <v>45199</v>
       </c>
       <c r="B28" t="n">
-        <v>1555001942.52095</v>
+        <v>1510557498.076506</v>
       </c>
       <c r="C28" t="n">
-        <v>1136419275.783821</v>
+        <v>1096717886.894932</v>
       </c>
     </row>
     <row r="29">
@@ -753,10 +753,10 @@
         <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>1764281212.922997</v>
+        <v>1697614546.25633</v>
       </c>
       <c r="C29" t="n">
-        <v>1268516498.006043</v>
+        <v>1209412331.339376</v>
       </c>
     </row>
     <row r="30">
@@ -764,10 +764,10 @@
         <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>2091461257.443465</v>
+        <v>2024794590.776798</v>
       </c>
       <c r="C30" t="n">
-        <v>1475318085.307631</v>
+        <v>1372880585.307631</v>
       </c>
     </row>
     <row r="31">
@@ -775,10 +775,10 @@
         <v>45473</v>
       </c>
       <c r="B31" t="n">
-        <v>2241674086.721243</v>
+        <v>2175007420.054576</v>
       </c>
       <c r="C31" t="n">
-        <v>1710698202.266695</v>
+        <v>1608260702.266695</v>
       </c>
     </row>
     <row r="32">
@@ -786,10 +786,10 @@
         <v>45565</v>
       </c>
       <c r="B32" t="n">
-        <v>2156954863.538703</v>
+        <v>2090288196.872037</v>
       </c>
       <c r="C32" t="n">
-        <v>1653076320.180527</v>
+        <v>1617861042.402749</v>
       </c>
     </row>
     <row r="33">
@@ -797,10 +797,10 @@
         <v>45657</v>
       </c>
       <c r="B33" t="n">
-        <v>1870318880.545532</v>
+        <v>1803652213.878865</v>
       </c>
       <c r="C33" t="n">
-        <v>1518400183.059012</v>
+        <v>1516796016.392345</v>
       </c>
     </row>
     <row r="34">
@@ -808,10 +808,10 @@
         <v>45747</v>
       </c>
       <c r="B34" t="n">
-        <v>2088985447.640281</v>
+        <v>2155652114.306947</v>
       </c>
       <c r="C34" t="n">
-        <v>1339359184.841543</v>
+        <v>1337755018.174876</v>
       </c>
     </row>
     <row r="35">
@@ -819,10 +819,10 @@
         <v>45838</v>
       </c>
       <c r="B35" t="n">
-        <v>2361028395.008701</v>
+        <v>2527695061.675368</v>
       </c>
       <c r="C35" t="n">
-        <v>1340518907.063765</v>
+        <v>1377803629.285987</v>
       </c>
     </row>
     <row r="36">
@@ -830,10 +830,10 @@
         <v>45930</v>
       </c>
       <c r="B36" t="n">
-        <v>2165033593.964201</v>
+        <v>2331700260.630867</v>
       </c>
       <c r="C36" t="n">
-        <v>1233310706.815902</v>
+        <v>1290039873.482569</v>
       </c>
     </row>
   </sheetData>

--- a/plot/storage/output/ongoing/ongoing_tech_filter_q.xlsx
+++ b/plot/storage/output/ongoing/ongoing_tech_filter_q.xlsx
@@ -580,7 +580,7 @@
         <v>931556370.8124057</v>
       </c>
       <c r="C13" t="n">
-        <v>900432426.8236215</v>
+        <v>900432373.3513993</v>
       </c>
     </row>
     <row r="14">
@@ -591,7 +591,7 @@
         <v>969758985.1914907</v>
       </c>
       <c r="C14" t="n">
-        <v>1513589110.322248</v>
+        <v>1513588949.905581</v>
       </c>
     </row>
     <row r="15">
@@ -602,7 +602,7 @@
         <v>1009318335.691491</v>
       </c>
       <c r="C15" t="n">
-        <v>1542359463.77985</v>
+        <v>1542359303.363183</v>
       </c>
     </row>
     <row r="16">
@@ -613,7 +613,7 @@
         <v>1058952463.39784</v>
       </c>
       <c r="C16" t="n">
-        <v>1553090081.990973</v>
+        <v>1553089921.574306</v>
       </c>
     </row>
     <row r="17">
@@ -624,7 +624,7 @@
         <v>1002868033.14784</v>
       </c>
       <c r="C17" t="n">
-        <v>1442749626.21764</v>
+        <v>1442749465.800973</v>
       </c>
     </row>
     <row r="18">
@@ -635,7 +635,7 @@
         <v>1018639099.912637</v>
       </c>
       <c r="C18" t="n">
-        <v>1204648079.750338</v>
+        <v>1204647919.333672</v>
       </c>
     </row>
     <row r="19">
@@ -646,7 +646,7 @@
         <v>1236569142.875172</v>
       </c>
       <c r="C19" t="n">
-        <v>1220521095.623354</v>
+        <v>1220520935.206687</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>1229618031.764061</v>
       </c>
       <c r="C20" t="n">
-        <v>1288510234.593051</v>
+        <v>1288510074.176384</v>
       </c>
     </row>
     <row r="21">
@@ -668,7 +668,7 @@
         <v>1140514575.625172</v>
       </c>
       <c r="C21" t="n">
-        <v>1477218567.926384</v>
+        <v>1477218407.509718</v>
       </c>
     </row>
     <row r="22">
@@ -679,7 +679,7 @@
         <v>808374351.2661978</v>
       </c>
       <c r="C22" t="n">
-        <v>1152808311.516128</v>
+        <v>1152808151.099462</v>
       </c>
     </row>
     <row r="23">
@@ -690,7 +690,7 @@
         <v>1160876898.13689</v>
       </c>
       <c r="C23" t="n">
-        <v>770399004.5091351</v>
+        <v>770398844.0924685</v>
       </c>
     </row>
     <row r="24">
@@ -701,7 +701,7 @@
         <v>1240206827.678319</v>
       </c>
       <c r="C24" t="n">
-        <v>874723419.8028414</v>
+        <v>874723259.3861747</v>
       </c>
     </row>
     <row r="25">
@@ -712,7 +712,7 @@
         <v>1167219759.168345</v>
       </c>
       <c r="C25" t="n">
-        <v>840560706.9972858</v>
+        <v>840560600.0528414</v>
       </c>
     </row>
     <row r="26">
